--- a/intake_forms/031_small_business_development_center_intake_form--intake_forms.xlsx
+++ b/intake_forms/031_small_business_development_center_intake_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'business_planning_and_strategy'}</t>
+          <t>business_planning_and_strategy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Business Planning and Strategy'}</t>
+          <t>Business Planning and Strategy</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'market_research'}</t>
+          <t>market_research</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Market Research'}</t>
+          <t>Market Research</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'retail'}</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Retail'}</t>
+          <t>Retail</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'business_planning_and_strategy'}</t>
+          <t>business_planning_and_strategy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Business Planning and Strategy'}</t>
+          <t>Business Planning and Strategy</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'market_research'}</t>
+          <t>market_research</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Market Research'}</t>
+          <t>Market Research</t>
         </is>
       </c>
     </row>
@@ -951,29 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'financial_planning'}</t>
+          <t>financial_planning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Financial Planning'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sbdc_services_used_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'market_research'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Market Research'}</t>
+          <t>Financial Planning</t>
         </is>
       </c>
     </row>
